--- a/data/trans_dic/P15A-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P15A-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,56</t>
+          <t>1,4; 4,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,46</t>
+          <t>1,75; 5,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,34</t>
+          <t>0,98; 4,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,27</t>
+          <t>0,38; 2,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,19</t>
+          <t>1,23; 5,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,74</t>
+          <t>0,9; 5,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,92</t>
+          <t>0,82; 3,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,89</t>
+          <t>1,68; 3,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,12</t>
+          <t>1,68; 4,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,68</t>
+          <t>1,82; 4,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,34</t>
+          <t>1,18; 3,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,62</t>
+          <t>1,19; 2,66</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,24</t>
+          <t>2,05; 6,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,8</t>
+          <t>1,5; 4,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,19</t>
+          <t>0,52; 3,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,28</t>
+          <t>1,29; 5,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,39</t>
+          <t>0,55; 3,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,48</t>
+          <t>0,29; 3,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,9</t>
+          <t>1,67; 5,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,56</t>
+          <t>0,61; 2,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,05</t>
+          <t>1,53; 4,07</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,44</t>
+          <t>1,18; 3,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,83</t>
+          <t>1,54; 3,99</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,68</t>
+          <t>1,18; 3,34</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,56; 7,7</t>
+          <t>3,49; 7,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,49</t>
+          <t>1,56; 4,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,51</t>
+          <t>0,99; 3,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,56</t>
+          <t>0,64; 3,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,42</t>
+          <t>1,05; 6,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,99</t>
+          <t>0,78; 4,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 8,27</t>
+          <t>1,47; 8,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,64</t>
+          <t>1,71; 5,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,27; 6,58</t>
+          <t>3,31; 6,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,02</t>
+          <t>1,64; 3,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,88</t>
+          <t>1,37; 4,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 3,58</t>
+          <t>0,87; 3,4</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,19</t>
+          <t>2,21; 4,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,15</t>
+          <t>2,07; 4,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,29</t>
+          <t>1,5; 3,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,36</t>
+          <t>1,5; 3,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,34</t>
+          <t>2,33; 5,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,51</t>
+          <t>1,24; 3,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,17</t>
+          <t>0,53; 2,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,05</t>
+          <t>0,95; 3,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,2</t>
+          <t>2,53; 4,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 3,52</t>
+          <t>1,98; 3,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,21; 2,47</t>
+          <t>1,28; 2,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,86</t>
+          <t>1,41; 2,82</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,1</t>
+          <t>1,92; 6,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,44</t>
+          <t>1,52; 4,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,82</t>
+          <t>2,56; 5,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,44</t>
+          <t>2,07; 6,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,96</t>
+          <t>2,53; 5,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,97</t>
+          <t>2,32; 4,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,34</t>
+          <t>1,94; 4,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,88</t>
+          <t>2,34; 4,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,29</t>
+          <t>2,7; 5,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,21</t>
+          <t>2,2; 4,19</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,48</t>
+          <t>2,41; 4,5</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,94</t>
+          <t>2,61; 4,96</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,3; 8,67</t>
+          <t>3,3; 8,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,09; 4,75</t>
+          <t>1,08; 5,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,0; 8,83</t>
+          <t>2,77; 7,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,35</t>
+          <t>0,0; 5,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,22</t>
+          <t>1,47; 3,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,64</t>
+          <t>2,45; 4,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,83</t>
+          <t>1,74; 3,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 4,14</t>
+          <t>1,83; 3,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,72</t>
+          <t>2,09; 3,82</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,35; 4,4</t>
+          <t>2,47; 4,26</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,36</t>
+          <t>2,38; 4,47</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,48</t>
+          <t>1,56; 3,48</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,13; 4,45</t>
+          <t>3,13; 4,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 3,48</t>
+          <t>2,29; 3,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,2</t>
+          <t>2,11; 3,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,85</t>
+          <t>1,5; 2,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,21; 3,33</t>
+          <t>2,27; 3,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,39</t>
+          <t>2,24; 3,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,06</t>
+          <t>2,03; 3,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 3,07</t>
+          <t>1,97; 3,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,84; 3,73</t>
+          <t>2,81; 3,68</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,24</t>
+          <t>2,44; 3,28</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 2,96</t>
+          <t>2,19; 2,97</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 2,75</t>
+          <t>1,95; 2,78</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria</t>
+          <t>Población que ha tenido un accidente en los últimos tres meses que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7108; 21589</t>
+          <t>6609; 21244</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7313; 23858</t>
+          <t>7643; 25888</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3937; 18626</t>
+          <t>4200; 18270</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2002; 11449</t>
+          <t>1944; 10818</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3124; 15919</t>
+          <t>3771; 15862</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3608; 18064</t>
+          <t>2819; 18262</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2862; 13604</t>
+          <t>2862; 13692</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7681; 17402</t>
+          <t>7499; 17804</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12474; 32167</t>
+          <t>13095; 32452</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13916; 35184</t>
+          <t>13676; 35715</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9153; 25901</t>
+          <t>9197; 27118</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11201; 24970</t>
+          <t>11293; 25309</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7355; 22903</t>
+          <t>7537; 24161</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6103; 20114</t>
+          <t>6262; 19298</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2031; 12035</t>
+          <t>1977; 12357</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5663; 23897</t>
+          <t>5828; 24619</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1988; 12598</t>
+          <t>2047; 12760</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>981; 11778</t>
+          <t>971; 10775</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6156; 21960</t>
+          <t>6207; 21722</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2388; 9787</t>
+          <t>2320; 9219</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11343; 29920</t>
+          <t>11307; 30050</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9090; 26024</t>
+          <t>8933; 25561</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10816; 28707</t>
+          <t>11526; 29901</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10454; 30689</t>
+          <t>9823; 27905</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19301; 41758</t>
+          <t>18906; 40745</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9363; 28254</t>
+          <t>9827; 26799</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5013; 18306</t>
+          <t>5163; 17465</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2791; 23820</t>
+          <t>4297; 25141</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1792; 10775</t>
+          <t>1762; 10461</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1983; 12973</t>
+          <t>2031; 12918</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2236; 13733</t>
+          <t>2435; 14226</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2630; 9412</t>
+          <t>2859; 9591</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23232; 46761</t>
+          <t>23480; 47326</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14642; 35717</t>
+          <t>14546; 34281</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10456; 26665</t>
+          <t>9430; 27703</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6741; 29858</t>
+          <t>7291; 28363</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26935; 51898</t>
+          <t>27425; 53219</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24347; 48044</t>
+          <t>24018; 49385</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16868; 37850</t>
+          <t>17288; 38331</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15686; 34770</t>
+          <t>15510; 34131</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16584; 38111</t>
+          <t>16653; 36484</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9895; 26910</t>
+          <t>9507; 26983</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4174; 17949</t>
+          <t>4396; 17552</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9644; 29793</t>
+          <t>9317; 30655</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>48701; 82020</t>
+          <t>49402; 81119</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38697; 67705</t>
+          <t>38157; 68389</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23812; 48737</t>
+          <t>25378; 48112</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>28736; 57575</t>
+          <t>28292; 56846</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>7173; 21388</t>
+          <t>6738; 21347</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6869; 22682</t>
+          <t>7753; 22775</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15705; 36114</t>
+          <t>15889; 34904</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9172; 30599</t>
+          <t>9843; 31565</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14676; 33869</t>
+          <t>14400; 32254</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17199; 37875</t>
+          <t>17638; 37950</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13978; 32026</t>
+          <t>14336; 33489</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19916; 41039</t>
+          <t>19672; 41431</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24857; 48655</t>
+          <t>24796; 47843</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27692; 53597</t>
+          <t>27996; 53244</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33306; 60928</t>
+          <t>32816; 61176</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>34440; 64981</t>
+          <t>34423; 65254</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9848; 25869</t>
+          <t>9849; 26073</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2910; 12687</t>
+          <t>2881; 13800</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8614; 25345</t>
+          <t>7960; 22624</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 12874</t>
+          <t>0; 12528</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19469; 40232</t>
+          <t>18363; 40836</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27246; 51423</t>
+          <t>27166; 52671</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19699; 41455</t>
+          <t>18851; 42403</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>14006; 31499</t>
+          <t>13969; 30109</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>32115; 57493</t>
+          <t>32297; 59122</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>32386; 60592</t>
+          <t>34032; 58602</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31436; 59745</t>
+          <t>32653; 61158</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15331; 34854</t>
+          <t>15679; 34866</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>102351; 145658</t>
+          <t>102509; 146844</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>79385; 118978</t>
+          <t>78337; 119118</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>71052; 108358</t>
+          <t>71403; 108373</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53568; 96325</t>
+          <t>50777; 93159</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>74598; 112575</t>
+          <t>76539; 115494</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>79383; 120371</t>
+          <t>79636; 121801</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>68556; 108213</t>
+          <t>71784; 109264</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>71881; 109982</t>
+          <t>70314; 109521</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>188744; 248000</t>
+          <t>186866; 244476</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>169743; 226057</t>
+          <t>170310; 228484</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>150940; 204937</t>
+          <t>151441; 205354</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>134999; 191406</t>
+          <t>135318; 193373</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15A-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P15A-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,14 +684,14 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>2,94%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>2,61%</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>2,99%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,48</t>
+          <t>1,4; 4,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,92</t>
+          <t>1,8; 5,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,26</t>
+          <t>0,92; 4,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,14</t>
+          <t>0,4; 2,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,17</t>
+          <t>0,97; 5,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,81</t>
+          <t>1,13; 5,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,95</t>
+          <t>0,82; 4,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,98</t>
+          <t>1,92; 4,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,16</t>
+          <t>1,63; 3,85</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,75</t>
+          <t>1,78; 4,71</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,49</t>
+          <t>1,19; 3,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,66</t>
+          <t>1,32; 2,79</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 6,58</t>
+          <t>2,01; 6,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,61</t>
+          <t>1,47; 4,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,28</t>
+          <t>0,53; 3,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,44</t>
+          <t>1,31; 5,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,43</t>
+          <t>0,51; 3,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,19</t>
+          <t>0,29; 3,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,84</t>
+          <t>1,69; 5,66</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,41</t>
+          <t>0,63; 2,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,07</t>
+          <t>1,56; 4,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,38</t>
+          <t>1,17; 3,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,54; 3,99</t>
+          <t>1,43; 3,81</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,34</t>
+          <t>1,27; 3,48</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 7,51</t>
+          <t>3,47; 7,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,26</t>
+          <t>1,56; 4,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,35</t>
+          <t>0,96; 3,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,76</t>
+          <t>1,71; 5,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,24</t>
+          <t>1,15; 6,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,97</t>
+          <t>0,77; 5,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 8,56</t>
+          <t>1,87; 8,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,75</t>
+          <t>1,39; 5,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,66</t>
+          <t>3,36; 6,65</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,85</t>
+          <t>1,62; 3,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,03</t>
+          <t>1,42; 3,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,4</t>
+          <t>1,99; 4,83</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,3</t>
+          <t>2,23; 4,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,26</t>
+          <t>2,2; 4,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,33</t>
+          <t>1,47; 3,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,3</t>
+          <t>1,55; 3,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,11</t>
+          <t>2,32; 5,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,52</t>
+          <t>1,31; 3,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,13</t>
+          <t>0,48; 2,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,13</t>
+          <t>1,69; 3,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,15</t>
+          <t>2,51; 4,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,98; 3,55</t>
+          <t>2,07; 3,61</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,44</t>
+          <t>1,28; 2,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,82</t>
+          <t>1,82; 3,24</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,09</t>
+          <t>1,86; 6,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,46</t>
+          <t>1,36; 4,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,62</t>
+          <t>2,59; 5,78</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,64</t>
+          <t>1,71; 5,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,67</t>
+          <t>2,7; 5,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,98</t>
+          <t>2,32; 5,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,54</t>
+          <t>1,95; 4,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,92</t>
+          <t>2,72; 5,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,2</t>
+          <t>2,74; 5,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,19</t>
+          <t>2,23; 4,26</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,5</t>
+          <t>2,46; 4,49</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,61; 4,96</t>
+          <t>2,65; 4,87</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,3; 8,74</t>
+          <t>3,25; 8,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 5,17</t>
+          <t>1,07; 4,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,88</t>
+          <t>2,78; 8,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,21</t>
+          <t>0,0; 5,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,27</t>
+          <t>1,54; 3,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,75</t>
+          <t>2,43; 4,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,92</t>
+          <t>1,86; 4,08</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,95</t>
+          <t>1,71; 3,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,82</t>
+          <t>2,07; 3,77</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,26</t>
+          <t>2,35; 4,3</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,38; 4,47</t>
+          <t>2,31; 4,42</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,48</t>
+          <t>1,45; 3,32</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,27 +1524,27 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>2,54%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,13; 4,49</t>
+          <t>3,11; 4,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 3,48</t>
+          <t>2,33; 3,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,2</t>
+          <t>2,13; 3,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,76</t>
+          <t>1,82; 3,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,42</t>
+          <t>2,24; 3,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,43</t>
+          <t>2,22; 3,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,09</t>
+          <t>1,91; 3,08</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,06</t>
+          <t>2,3; 3,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,81; 3,68</t>
+          <t>2,8; 3,69</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,44; 3,28</t>
+          <t>2,42; 3,23</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 2,97</t>
+          <t>2,17; 2,93</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 2,78</t>
+          <t>2,21; 2,97</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5137</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11697</t>
+          <t>14338</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16834</t>
+          <t>20401</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6609; 21244</t>
+          <t>6611; 20975</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7643; 25888</t>
+          <t>7859; 24307</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4200; 18270</t>
+          <t>3951; 18213</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1944; 10818</t>
+          <t>2189; 12367</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3771; 15862</t>
+          <t>2971; 15843</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2819; 18262</t>
+          <t>3544; 18661</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2862; 13692</t>
+          <t>2843; 13884</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7499; 17804</t>
+          <t>9381; 22650</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13095; 32452</t>
+          <t>12711; 30013</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13676; 35715</t>
+          <t>13370; 35412</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9197; 27118</t>
+          <t>9269; 26212</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11293; 25309</t>
+          <t>13668; 28947</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>12773</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16805</t>
+          <t>18549</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7537; 24161</t>
+          <t>7387; 22169</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6262; 19298</t>
+          <t>6140; 20221</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1977; 12357</t>
+          <t>2014; 12729</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5828; 24619</t>
+          <t>6342; 24765</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2047; 12760</t>
+          <t>1911; 11952</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>971; 10775</t>
+          <t>987; 12243</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6207; 21722</t>
+          <t>6287; 21080</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2320; 9219</t>
+          <t>2661; 9638</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11307; 30050</t>
+          <t>11555; 29945</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8933; 25561</t>
+          <t>8872; 25713</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11526; 29901</t>
+          <t>10683; 28577</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9823; 27905</t>
+          <t>11481; 31506</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>14779</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17607</t>
+          <t>20315</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18906; 40745</t>
+          <t>18845; 39319</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9827; 26799</t>
+          <t>9838; 27218</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5163; 17465</t>
+          <t>5016; 18161</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4297; 25141</t>
+          <t>8057; 23981</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1762; 10461</t>
+          <t>1933; 11204</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2031; 12918</t>
+          <t>2015; 14390</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2435; 14226</t>
+          <t>3108; 14485</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2859; 9591</t>
+          <t>2603; 10058</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23480; 47326</t>
+          <t>23831; 47224</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14546; 34281</t>
+          <t>14385; 34303</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9430; 27703</t>
+          <t>9794; 26298</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7291; 28363</t>
+          <t>13147; 31813</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23186</t>
+          <t>27162</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>19275</t>
+          <t>21092</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>42461</t>
+          <t>48254</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27425; 53219</t>
+          <t>27663; 53948</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>24018; 49385</t>
+          <t>25499; 50612</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17288; 38331</t>
+          <t>16936; 38573</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15510; 34131</t>
+          <t>17599; 38337</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16653; 36484</t>
+          <t>16588; 36379</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9507; 26983</t>
+          <t>10019; 26598</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4396; 17552</t>
+          <t>3941; 17349</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9317; 30655</t>
+          <t>14568; 31079</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49402; 81119</t>
+          <t>48998; 80747</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38157; 68389</t>
+          <t>39833; 69557</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25378; 48112</t>
+          <t>25209; 47897</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>28292; 56846</t>
+          <t>36358; 64623</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17519</t>
+          <t>18261</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>29145</t>
+          <t>30782</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>46663</t>
+          <t>49043</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>6738; 21347</t>
+          <t>6536; 21361</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7753; 22775</t>
+          <t>6961; 22424</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15889; 34904</t>
+          <t>16073; 35866</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9843; 31565</t>
+          <t>9740; 32218</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14400; 32254</t>
+          <t>15355; 33833</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>17638; 37950</t>
+          <t>17702; 38592</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14336; 33489</t>
+          <t>14359; 33442</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19672; 41431</t>
+          <t>22619; 43760</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24796; 47843</t>
+          <t>25157; 48302</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27996; 53244</t>
+          <t>28364; 54234</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>32816; 61176</t>
+          <t>33456; 61021</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>34423; 65254</t>
+          <t>37089; 68116</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>20302</t>
+          <t>20592</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>22582</t>
+          <t>23100</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>9849; 26073</t>
+          <t>9702; 25941</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2881; 13800</t>
+          <t>2861; 13104</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7960; 22624</t>
+          <t>7971; 24009</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 12528</t>
+          <t>0; 13966</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18363; 40836</t>
+          <t>19275; 41154</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27166; 52671</t>
+          <t>26979; 51426</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18851; 42403</t>
+          <t>20106; 44136</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>13969; 30109</t>
+          <t>14466; 31026</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>32297; 59122</t>
+          <t>32092; 58262</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>34032; 58602</t>
+          <t>32319; 59180</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32653; 61158</t>
+          <t>31635; 60519</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15679; 34866</t>
+          <t>15714; 35856</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>72217</t>
+          <t>81546</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>90736</t>
+          <t>98116</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>162953</t>
+          <t>179663</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>102509; 146844</t>
+          <t>101649; 144964</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>78337; 119118</t>
+          <t>79744; 119985</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>71403; 108373</t>
+          <t>72284; 110049</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50777; 93159</t>
+          <t>62592; 103778</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>76539; 115494</t>
+          <t>75605; 114931</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>79636; 121801</t>
+          <t>78777; 119075</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>71784; 109264</t>
+          <t>67355; 108799</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>70314; 109521</t>
+          <t>83482; 118874</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>186866; 244476</t>
+          <t>186476; 245509</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>170310; 228484</t>
+          <t>168793; 224879</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>151441; 205354</t>
+          <t>150331; 202750</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>135318; 193373</t>
+          <t>156166; 209859</t>
         </is>
       </c>
     </row>
